--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3028-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3028-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{824DBEBA-3D4B-4DDD-BD9D-11D888158897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63E151DA-0AF5-4CAD-B2AC-79FA25C202E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{CCD0ABEA-75E5-454D-BD43-32A4985618C9}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{29C227ED-DAFD-494A-9703-39C2FA22B251}"/>
   </bookViews>
   <sheets>
     <sheet name="3028-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1490,27 +1490,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE020B2D-E94F-461F-AA3F-B2B24CBFB33E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0AEFFA-32BE-4B0E-A764-348A697A1AB5}">
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1544,7 +1543,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1580,7 +1579,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1632,7 +1631,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1700,7 +1699,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1772,7 +1771,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1844,7 +1843,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1916,7 +1915,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -1988,7 +1987,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2060,7 +2059,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2019</v>
       </c>
@@ -2132,7 +2131,7 @@
         <v>6.52</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2018</v>
       </c>
@@ -2204,7 +2203,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2017</v>
       </c>
@@ -2276,7 +2275,7 @@
         <v>9.48</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2016</v>
       </c>
@@ -2348,7 +2347,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2015</v>
       </c>
@@ -2420,7 +2419,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>2014</v>
       </c>
@@ -2492,7 +2491,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2013</v>
       </c>
@@ -2564,7 +2563,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2012</v>
       </c>
@@ -2636,7 +2635,7 @@
         <v>7.44</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2011</v>
       </c>
@@ -2708,7 +2707,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2010</v>
       </c>
@@ -2780,7 +2779,7 @@
         <v>9.89</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2009</v>
       </c>
@@ -2852,7 +2851,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2008</v>
       </c>
@@ -2924,7 +2923,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2007</v>
       </c>
@@ -2996,7 +2995,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2006</v>
       </c>
@@ -3068,7 +3067,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2005</v>
       </c>
@@ -3140,7 +3139,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2004</v>
       </c>
@@ -3212,7 +3211,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2003</v>
       </c>
@@ -3284,7 +3283,7 @@
         <v>9.7200000000000006</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2002</v>
       </c>
@@ -3356,7 +3355,7 @@
         <v>6.52</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2001</v>
       </c>
@@ -3428,7 +3427,7 @@
         <v>8.58</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2000</v>
       </c>
@@ -3500,7 +3499,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>1999</v>
       </c>
@@ -3572,7 +3571,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>1998</v>
       </c>
@@ -3644,7 +3643,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1997</v>
       </c>
@@ -3716,7 +3715,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35" t="s">
         <v>54</v>
       </c>
